--- a/ecv/extraccion_ecv_2023/ecv_2023_wide.xlsx
+++ b/ecv/extraccion_ecv_2023/ecv_2023_wide.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:X12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -402,741 +402,819 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>dep_economica_total</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>IMCV_urbano</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>estrato_urbano</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>calidad_vivienda_urbano</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>num_servicios_pub_urbano</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>num_servicios_suspendidos_urbano</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>tasa_desempleo_urbano</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>dep_economica_urbano</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>IMCV_rural</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>estrato_rural</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>calidad_vivienda_rural</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>num_servicios_pub_rural</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>num_servicios_suspendidos_rural</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>tasa_desempleo_rural</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dep_economica_rural</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>05837</t>
+          <t>05045</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Turbo</t>
+          <t>Apartadó</t>
         </is>
       </c>
       <c r="C2">
         <v>2023</v>
       </c>
       <c r="D2">
-        <v>26.3862146175341</v>
+        <v>30.6806003893439</v>
       </c>
       <c r="E2">
-        <v>0.138868407899854</v>
+        <v>0.336840871594346</v>
       </c>
       <c r="F2">
-        <v>0.256780748576993</v>
+        <v>0.527186599971133</v>
       </c>
       <c r="G2">
-        <v>0.668866477097125</v>
+        <v>1.52120783760815</v>
       </c>
       <c r="H2">
-        <v>1.42901143402215</v>
+        <v>1.4769264263316</v>
       </c>
       <c r="I2">
-        <v>19.8643719691351</v>
+        <v>8.05231791816083</v>
       </c>
       <c r="J2">
-        <v>28.1947088709677</v>
+        <v>45.7996292433601</v>
       </c>
       <c r="K2">
-        <v>0.240760317460317</v>
+        <v>30.8545153846154</v>
       </c>
       <c r="L2">
-        <v>0.374820105820106</v>
+        <v>0.378445</v>
       </c>
       <c r="M2">
-        <v>1.07158941798942</v>
+        <v>0.56903375</v>
       </c>
       <c r="N2">
-        <v>1.38929153439153</v>
+        <v>1.60716625</v>
       </c>
       <c r="O2">
-        <v>26.3001152239321</v>
+        <v>1.47278375</v>
       </c>
       <c r="P2">
-        <v>25.2214457142857</v>
+        <v>8.231071925467059</v>
       </c>
       <c r="Q2">
-        <v>0.0520710743801653</v>
+        <v>44.6552506866898</v>
+      </c>
+      <c r="R2">
+        <v>29.6414093333333</v>
       </c>
       <c r="S2">
-        <v>0.325804132231405</v>
-      </c>
-      <c r="T2">
-        <v>1.46284710743802</v>
+        <v>0.0739845360824742</v>
       </c>
       <c r="U2">
-        <v>12.3347781741317</v>
+        <v>0.978119587628866</v>
+      </c>
+      <c r="V2">
+        <v>1.5031</v>
+      </c>
+      <c r="W2">
+        <v>6.65772671571826</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>05873</t>
+          <t>05051</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Vigía del Fuerte</t>
+          <t>Arboletes</t>
         </is>
       </c>
       <c r="C3">
         <v>2023</v>
       </c>
       <c r="D3">
-        <v>26.766024501412</v>
+        <v>24.1015139361819</v>
       </c>
       <c r="E3">
-        <v>0.0593503022286841</v>
+        <v>0.0396308599302219</v>
+      </c>
+      <c r="G3">
+        <v>0.427351884382883</v>
       </c>
       <c r="H3">
-        <v>1.27691475821705</v>
+        <v>1.49905406579049</v>
       </c>
       <c r="I3">
-        <v>11.9389222251462</v>
+        <v>11.3569438266688</v>
       </c>
       <c r="J3">
-        <v>28.4168866666667</v>
+        <v>62.9031708148653</v>
       </c>
       <c r="K3">
-        <v>0.0797823529411765</v>
+        <v>24.8124649635037</v>
+      </c>
+      <c r="L3">
+        <v>0.0434524137931035</v>
       </c>
       <c r="N3">
-        <v>1.08504411764706</v>
+        <v>0.998806206896552</v>
       </c>
       <c r="O3">
-        <v>12.0317802319202</v>
+        <v>1.49350275862069</v>
       </c>
       <c r="P3">
-        <v>25.7396730769231</v>
+        <v>15.1790927468417</v>
       </c>
       <c r="Q3">
-        <v>0.0437541666666667</v>
-      </c>
-      <c r="T3">
-        <v>1.42337291666667</v>
-      </c>
-      <c r="U3">
-        <v>11.8766557296205</v>
+        <v>52.7423683327743</v>
+      </c>
+      <c r="R3">
+        <v>23.5077787234043</v>
+      </c>
+      <c r="S3">
+        <v>0.0368456140350877</v>
+      </c>
+      <c r="V3">
+        <v>1.5031</v>
+      </c>
+      <c r="W3">
+        <v>8.39483352733051</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>05045</t>
+          <t>05147</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Apartadó</t>
+          <t>Carepa</t>
         </is>
       </c>
       <c r="C4">
         <v>2023</v>
       </c>
       <c r="D4">
-        <v>30.6806003893439</v>
+        <v>31.2584988476185</v>
       </c>
       <c r="E4">
-        <v>0.336840871594346</v>
+        <v>0.424977925202123</v>
       </c>
       <c r="F4">
-        <v>0.527186599971133</v>
+        <v>0.623705256451155</v>
       </c>
       <c r="G4">
-        <v>1.52120783760815</v>
+        <v>1.27130908523232</v>
       </c>
       <c r="H4">
-        <v>1.4769264263316</v>
+        <v>1.48371240068798</v>
       </c>
       <c r="I4">
-        <v>8.05231791816083</v>
+        <v>15.1318753281131</v>
       </c>
       <c r="J4">
-        <v>30.8545153846154</v>
+        <v>50.0350985984467</v>
       </c>
       <c r="K4">
-        <v>0.378445</v>
+        <v>32.5036594202899</v>
       </c>
       <c r="L4">
-        <v>0.56903375</v>
+        <v>0.5021476635514019</v>
       </c>
       <c r="M4">
-        <v>1.60716625</v>
+        <v>0.718818691588785</v>
       </c>
       <c r="N4">
-        <v>1.47278375</v>
+        <v>1.44878691588785</v>
       </c>
       <c r="O4">
-        <v>8.231071925467059</v>
+        <v>1.48359158878505</v>
       </c>
       <c r="P4">
-        <v>29.6414093333333</v>
-      </c>
-      <c r="Q4">
-        <v>0.0739845360824742</v>
+        <v>14.9101534936639</v>
+      </c>
+      <c r="R4">
+        <v>26.8371426470588</v>
       </c>
       <c r="S4">
-        <v>0.978119587628866</v>
-      </c>
-      <c r="T4">
-        <v>1.5031</v>
+        <v>0.162297272727273</v>
       </c>
       <c r="U4">
-        <v>6.65772671571826</v>
+        <v>0.667186363636364</v>
+      </c>
+      <c r="V4">
+        <v>1.48412363636364</v>
+      </c>
+      <c r="W4">
+        <v>15.9300872399264</v>
+      </c>
+      <c r="X4">
+        <v>55.4289710231494</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>05051</t>
+          <t>05172</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Arboletes</t>
+          <t>Chigorodó</t>
         </is>
       </c>
       <c r="C5">
         <v>2023</v>
       </c>
       <c r="D5">
-        <v>24.1015139361819</v>
+        <v>29.7674633356154</v>
       </c>
       <c r="E5">
-        <v>0.0396308599302219</v>
+        <v>0.385382706996069</v>
+      </c>
+      <c r="F5">
+        <v>0.595501454508135</v>
       </c>
       <c r="G5">
-        <v>0.427351884382883</v>
+        <v>1.31013475052247</v>
       </c>
       <c r="H5">
-        <v>1.49905406579049</v>
+        <v>1.48808916318356</v>
       </c>
       <c r="I5">
-        <v>11.3569438266688</v>
+        <v>9.655855192631631</v>
       </c>
       <c r="J5">
-        <v>24.8124649635037</v>
+        <v>52.2779665030074</v>
       </c>
       <c r="K5">
-        <v>0.0434524137931035</v>
+        <v>30.2846075268817</v>
+      </c>
+      <c r="L5">
+        <v>0.438865151515151</v>
       </c>
       <c r="M5">
-        <v>0.998806206896552</v>
+        <v>0.6603196969696969</v>
       </c>
       <c r="N5">
-        <v>1.49350275862069</v>
+        <v>1.48304621212121</v>
       </c>
       <c r="O5">
-        <v>15.1790927468417</v>
+        <v>1.48728636363636</v>
       </c>
       <c r="P5">
-        <v>23.5077787234043</v>
+        <v>10.2535701754016</v>
       </c>
       <c r="Q5">
-        <v>0.0368456140350877</v>
-      </c>
-      <c r="T5">
-        <v>1.5031</v>
-      </c>
-      <c r="U5">
-        <v>8.39483352733051</v>
+        <v>49.6712112701628</v>
+      </c>
+      <c r="R5">
+        <v>26.7549844827586</v>
+      </c>
+      <c r="S5">
+        <v>0.0291694444444444</v>
+      </c>
+      <c r="V5">
+        <v>1.49343611111111</v>
+      </c>
+      <c r="W5">
+        <v>5.84778645295824</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>05147</t>
+          <t>05475</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Carepa</t>
+          <t>Murindó</t>
         </is>
       </c>
       <c r="C6">
         <v>2023</v>
       </c>
       <c r="D6">
-        <v>31.2584988476185</v>
+        <v>26.5723724775803</v>
       </c>
       <c r="E6">
-        <v>0.424977925202123</v>
-      </c>
-      <c r="F6">
-        <v>0.623705256451155</v>
-      </c>
-      <c r="G6">
-        <v>1.27130908523232</v>
+        <v>0.0409192829984558</v>
       </c>
       <c r="H6">
-        <v>1.48371240068798</v>
+        <v>1.46440871121526</v>
       </c>
       <c r="I6">
-        <v>15.1318753281131</v>
+        <v>9.189549059907259</v>
       </c>
       <c r="J6">
-        <v>32.5036594202899</v>
+        <v>91.5327227512586</v>
       </c>
       <c r="K6">
-        <v>0.5021476635514019</v>
+        <v>27.4968315789474</v>
       </c>
       <c r="L6">
-        <v>0.718818691588785</v>
-      </c>
-      <c r="M6">
-        <v>1.44878691588785</v>
+        <v>0.03937875</v>
       </c>
       <c r="N6">
-        <v>1.48359158878505</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>14.9101534936639</v>
+        <v>1.485705</v>
       </c>
       <c r="P6">
-        <v>26.8371426470588</v>
-      </c>
-      <c r="Q6">
-        <v>0.162297272727273</v>
+        <v>10.2455145697455</v>
+      </c>
+      <c r="R6">
+        <v>25.4548705882353</v>
       </c>
       <c r="S6">
-        <v>0.667186363636364</v>
-      </c>
-      <c r="T6">
-        <v>1.48412363636364</v>
-      </c>
-      <c r="U6">
-        <v>15.9300872399264</v>
+        <v>0.0426282051282051</v>
+      </c>
+      <c r="V6">
+        <v>1.44078461538462</v>
+      </c>
+      <c r="W6">
+        <v>8.16679070239802</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>05172</t>
+          <t>05480</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Chigorodó</t>
+          <t>Mutatá</t>
         </is>
       </c>
       <c r="C7">
         <v>2023</v>
       </c>
       <c r="D7">
-        <v>29.7674633356154</v>
+        <v>27.7091438971389</v>
       </c>
       <c r="E7">
-        <v>0.385382706996069</v>
+        <v>0.0375532263186222</v>
       </c>
       <c r="F7">
-        <v>0.595501454508135</v>
+        <v>0.177864110333692</v>
       </c>
       <c r="G7">
-        <v>1.31013475052247</v>
+        <v>0.577010205520529</v>
       </c>
       <c r="H7">
-        <v>1.48808916318356</v>
+        <v>1.48707452544979</v>
       </c>
       <c r="I7">
-        <v>9.655855192631631</v>
-      </c>
-      <c r="J7">
-        <v>30.2846075268817</v>
+        <v>4.57508558230136</v>
       </c>
       <c r="K7">
-        <v>0.438865151515151</v>
+        <v>26.7433301204819</v>
       </c>
       <c r="L7">
-        <v>0.6603196969696969</v>
-      </c>
-      <c r="M7">
-        <v>1.48304621212121</v>
+        <v>0.06563125</v>
       </c>
       <c r="N7">
-        <v>1.48728636363636</v>
+        <v>0.848980357142857</v>
       </c>
       <c r="O7">
-        <v>10.2535701754016</v>
+        <v>1.47833928571429</v>
       </c>
       <c r="P7">
-        <v>26.7549844827586</v>
+        <v>6.89233390831209</v>
       </c>
       <c r="Q7">
-        <v>0.0291694444444444</v>
+        <v>52.5000936364658</v>
+      </c>
+      <c r="R7">
+        <v>28.6670350877193</v>
+      </c>
+      <c r="S7">
+        <v>0.0123541176470588</v>
       </c>
       <c r="T7">
-        <v>1.49343611111111</v>
+        <v>0.178583529411765</v>
       </c>
       <c r="U7">
-        <v>5.84778645295824</v>
+        <v>0.332925882352941</v>
+      </c>
+      <c r="V7">
+        <v>1.49491411764706</v>
+      </c>
+      <c r="W7">
+        <v>2.7900886540493</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>05475</t>
+          <t>05490</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Murindó</t>
+          <t>Necoclí</t>
         </is>
       </c>
       <c r="C8">
         <v>2023</v>
       </c>
       <c r="D8">
-        <v>26.5723724775803</v>
+        <v>26.5425411409584</v>
       </c>
       <c r="E8">
-        <v>0.0409192829984558</v>
+        <v>0.0402342692419565</v>
+      </c>
+      <c r="F8">
+        <v>0.194485930323529</v>
+      </c>
+      <c r="G8">
+        <v>0.864093032282313</v>
       </c>
       <c r="H8">
-        <v>1.46440871121526</v>
+        <v>1.43713277591285</v>
       </c>
       <c r="I8">
-        <v>9.189549059907259</v>
+        <v>15.8538584641096</v>
       </c>
       <c r="J8">
-        <v>27.4968315789474</v>
+        <v>64.1923207697776</v>
       </c>
       <c r="K8">
-        <v>0.03937875</v>
+        <v>27.5950177419355</v>
+      </c>
+      <c r="L8">
+        <v>0.033513829787234</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>0.221562765957447</v>
       </c>
       <c r="N8">
-        <v>1.485705</v>
+        <v>1.24212872340426</v>
       </c>
       <c r="O8">
-        <v>10.2455145697455</v>
+        <v>1.42188936170213</v>
       </c>
       <c r="P8">
-        <v>25.4548705882353</v>
+        <v>18.0706089453563</v>
       </c>
       <c r="Q8">
-        <v>0.0426282051282051</v>
-      </c>
-      <c r="T8">
-        <v>1.44078461538462</v>
+        <v>50.626988583193</v>
+      </c>
+      <c r="R8">
+        <v>26.0486113207547</v>
+      </c>
+      <c r="S8">
+        <v>0.0437541666666667</v>
       </c>
       <c r="U8">
-        <v>8.16679070239802</v>
+        <v>0.666093055555556</v>
+      </c>
+      <c r="V8">
+        <v>1.44511666666667</v>
+      </c>
+      <c r="W8">
+        <v>14.4243661126115</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>05480</t>
+          <t>05659</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Mutatá</t>
+          <t>San Juan de Urabá</t>
         </is>
       </c>
       <c r="C9">
         <v>2023</v>
       </c>
       <c r="D9">
-        <v>27.7091438971389</v>
+        <v>26.4360286586077</v>
       </c>
       <c r="E9">
-        <v>0.0375532263186222</v>
-      </c>
-      <c r="F9">
-        <v>0.177864110333692</v>
+        <v>0.108185903177744</v>
       </c>
       <c r="G9">
-        <v>0.577010205520529</v>
+        <v>0.70140146190401</v>
       </c>
       <c r="H9">
-        <v>1.48707452544979</v>
+        <v>1.48591011129753</v>
       </c>
       <c r="I9">
-        <v>4.57508558230136</v>
+        <v>5.32156500520407</v>
       </c>
       <c r="J9">
-        <v>26.7433301204819</v>
+        <v>64.8679678530425</v>
       </c>
       <c r="K9">
-        <v>0.06563125</v>
-      </c>
-      <c r="M9">
-        <v>0.848980357142857</v>
+        <v>26.8598215053763</v>
+      </c>
+      <c r="L9">
+        <v>0.117826732673267</v>
       </c>
       <c r="N9">
-        <v>1.47833928571429</v>
+        <v>1.06475940594059</v>
       </c>
       <c r="O9">
-        <v>6.89233390831209</v>
+        <v>1.46176534653465</v>
       </c>
       <c r="P9">
-        <v>28.6670350877193</v>
+        <v>8.99162368253867</v>
       </c>
       <c r="Q9">
-        <v>0.0123541176470588</v>
+        <v>56.9532602423543</v>
       </c>
       <c r="R9">
-        <v>0.178583529411765</v>
+        <v>26.1459956043956</v>
       </c>
       <c r="S9">
-        <v>0.332925882352941</v>
-      </c>
-      <c r="T9">
-        <v>1.49491411764706</v>
+        <v>0.101322105263158</v>
       </c>
       <c r="U9">
-        <v>2.7900886540493</v>
+        <v>0.442708421052632</v>
+      </c>
+      <c r="V9">
+        <v>1.5031</v>
+      </c>
+      <c r="W9">
+        <v>2.74741657315379</v>
+      </c>
+      <c r="X9">
+        <v>70.0991609458429</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>05490</t>
+          <t>05665</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Necoclí</t>
+          <t>San Pedro de Urabá</t>
         </is>
       </c>
       <c r="C10">
         <v>2023</v>
       </c>
       <c r="D10">
-        <v>26.5425411409584</v>
+        <v>25.8545424154964</v>
       </c>
       <c r="E10">
-        <v>0.0402342692419565</v>
+        <v>0.0201098477140144</v>
       </c>
       <c r="F10">
-        <v>0.194485930323529</v>
+        <v>0.158347512749131</v>
       </c>
       <c r="G10">
-        <v>0.864093032282313</v>
+        <v>0.822277523750562</v>
       </c>
       <c r="H10">
-        <v>1.43713277591285</v>
+        <v>1.47960684947768</v>
       </c>
       <c r="I10">
-        <v>15.8538584641096</v>
+        <v>4.41390417567865</v>
       </c>
       <c r="J10">
-        <v>27.5950177419355</v>
+        <v>56.8011516387973</v>
       </c>
       <c r="K10">
-        <v>0.033513829787234</v>
+        <v>26.8033303797468</v>
       </c>
       <c r="L10">
-        <v>0.221562765957447</v>
-      </c>
-      <c r="M10">
-        <v>1.24212872340426</v>
+        <v>0.0395833333333333</v>
       </c>
       <c r="N10">
-        <v>1.42188936170213</v>
+        <v>1.37277142857143</v>
       </c>
       <c r="O10">
-        <v>18.0706089453563</v>
+        <v>1.49481666666667</v>
       </c>
       <c r="P10">
-        <v>26.0486113207547</v>
+        <v>6.72970290167189</v>
       </c>
       <c r="Q10">
-        <v>0.0437541666666667</v>
+        <v>53.2476658969983</v>
+      </c>
+      <c r="R10">
+        <v>24.8632621212121</v>
       </c>
       <c r="S10">
-        <v>0.666093055555556</v>
+        <v>0</v>
       </c>
       <c r="T10">
-        <v>1.44511666666667</v>
-      </c>
-      <c r="U10">
-        <v>14.4243661126115</v>
+        <v>0.121542253521127</v>
+      </c>
+      <c r="V10">
+        <v>1.4639</v>
+      </c>
+      <c r="W10">
+        <v>2.63380237291733</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>05659</t>
+          <t>05837</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>San Juan de Urabá</t>
+          <t>Turbo</t>
         </is>
       </c>
       <c r="C11">
         <v>2023</v>
       </c>
       <c r="D11">
-        <v>26.4360286586077</v>
+        <v>26.3862146175341</v>
       </c>
       <c r="E11">
-        <v>0.108185903177744</v>
+        <v>0.138868407899854</v>
+      </c>
+      <c r="F11">
+        <v>0.256780748576993</v>
       </c>
       <c r="G11">
-        <v>0.70140146190401</v>
+        <v>0.668866477097125</v>
       </c>
       <c r="H11">
-        <v>1.48591011129753</v>
+        <v>1.42901143402215</v>
       </c>
       <c r="I11">
-        <v>5.32156500520407</v>
+        <v>19.8643719691351</v>
       </c>
       <c r="J11">
-        <v>26.8598215053763</v>
+        <v>59.5897187047741</v>
       </c>
       <c r="K11">
-        <v>0.117826732673267</v>
+        <v>28.1947088709677</v>
+      </c>
+      <c r="L11">
+        <v>0.240760317460317</v>
       </c>
       <c r="M11">
-        <v>1.06475940594059</v>
+        <v>0.374820105820106</v>
       </c>
       <c r="N11">
-        <v>1.46176534653465</v>
+        <v>1.07158941798942</v>
       </c>
       <c r="O11">
-        <v>8.99162368253867</v>
+        <v>1.38929153439153</v>
       </c>
       <c r="P11">
-        <v>26.1459956043956</v>
+        <v>26.3001152239321</v>
       </c>
       <c r="Q11">
-        <v>0.101322105263158</v>
+        <v>55.5717152470912</v>
+      </c>
+      <c r="R11">
+        <v>25.2214457142857</v>
       </c>
       <c r="S11">
-        <v>0.442708421052632</v>
-      </c>
-      <c r="T11">
-        <v>1.5031</v>
+        <v>0.0520710743801653</v>
       </c>
       <c r="U11">
-        <v>2.74741657315379</v>
+        <v>0.325804132231405</v>
+      </c>
+      <c r="V11">
+        <v>1.46284710743802</v>
+      </c>
+      <c r="W11">
+        <v>12.3347781741317</v>
+      </c>
+      <c r="X11">
+        <v>62.871484343877</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>05665</t>
+          <t>05873</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>San Pedro de Urabá</t>
+          <t>Vigía del Fuerte</t>
         </is>
       </c>
       <c r="C12">
         <v>2023</v>
       </c>
       <c r="D12">
-        <v>25.8545424154964</v>
+        <v>26.766024501412</v>
       </c>
       <c r="E12">
-        <v>0.0201098477140144</v>
-      </c>
-      <c r="F12">
-        <v>0.158347512749131</v>
-      </c>
-      <c r="G12">
-        <v>0.822277523750562</v>
+        <v>0.0593503022286841</v>
       </c>
       <c r="H12">
-        <v>1.47960684947768</v>
+        <v>1.27691475821705</v>
       </c>
       <c r="I12">
-        <v>4.41390417567865</v>
+        <v>11.9389222251462</v>
       </c>
       <c r="J12">
-        <v>26.8033303797468</v>
+        <v>79.1906712014993</v>
       </c>
       <c r="K12">
-        <v>0.0395833333333333</v>
-      </c>
-      <c r="M12">
-        <v>1.37277142857143</v>
-      </c>
-      <c r="N12">
-        <v>1.49481666666667</v>
+        <v>28.4168866666667</v>
+      </c>
+      <c r="L12">
+        <v>0.0797823529411765</v>
       </c>
       <c r="O12">
-        <v>6.72970290167189</v>
+        <v>1.08504411764706</v>
       </c>
       <c r="P12">
-        <v>24.8632621212121</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
+        <v>12.0317802319202</v>
       </c>
       <c r="R12">
-        <v>0.121542253521127</v>
-      </c>
-      <c r="T12">
-        <v>1.4639</v>
-      </c>
-      <c r="U12">
-        <v>2.63380237291733</v>
+        <v>25.7396730769231</v>
+      </c>
+      <c r="S12">
+        <v>0.0437541666666667</v>
+      </c>
+      <c r="V12">
+        <v>1.42337291666667</v>
+      </c>
+      <c r="W12">
+        <v>11.8766557296205</v>
       </c>
     </row>
   </sheetData>
